--- a/per-stock/HPE/financials.xlsx
+++ b/per-stock/HPE/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43918868480</v>
+        <v>62780489728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60798869504</v>
+        <v>78853488640</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -560,10 +569,8 @@
           <t>Trailing P/E</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>(missing — see Data flags)</t>
-        </is>
+      <c r="B8" t="n">
+        <v>44.30841</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -578,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.14554</v>
+        <v>11.858815</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.2287405</v>
+        <v>1.6183041</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -608,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.32071</v>
+        <v>0.33776</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -623,7 +630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07643999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -638,7 +645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0033000002</v>
+        <v>0.040110003</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -653,7 +660,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.00471</v>
+        <v>0.06315</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -668,7 +675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.184</v>
+        <v>0.4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -683,7 +690,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4840999936</v>
+        <v>5292000256</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -698,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21660999680</v>
+        <v>21304000512</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -713,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2551500032</v>
+        <v>3989000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -728,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1326854089</v>
+        <v>1324203521</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -743,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33.1</v>
+        <v>47.41</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D52</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C52</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B52</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B51:E51)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D50</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C50</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B50</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B49:E49)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D41</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C41</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B41</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B41:E41)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1872,13 +2350,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1888,6 +2366,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1898,30 +2377,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -1934,21 +2418,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-8346000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-46800000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-86730000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-37800000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-294630000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>23635000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1957,10 +2442,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.21</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0.21</v>
@@ -1969,9 +2454,10 @@
         <v>0.21</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.145</v>
+        <v>0.21</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1980,21 +2466,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>1780000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1576000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>1698000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>1295000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>2271000000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>950000000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2003,21 +2490,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-78000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-117000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-413000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-180000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-1403000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>163000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2026,21 +2514,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-78000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-117000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-413000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-180000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-1403000000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>163000000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2049,21 +2538,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>624000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>452000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>305000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-1050000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>627000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2072,21 +2562,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>877000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>872000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>877000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>687000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>574000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>599000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2095,21 +2586,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>6224000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>5400000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>5871000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>5903000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>4921000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>4998000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2118,21 +2610,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>1702000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1459000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>1285000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>1115000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>868000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>1113000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2141,21 +2634,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>825000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>587000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>408000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>428000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>294000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>514000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2164,21 +2658,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-73000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-54000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-261000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>8000000</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>39000000</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>39000000</v>
       </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2188,12 +2683,13 @@
       </c>
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2202,21 +2698,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>693654000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>522200000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>501270000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>447200000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>58370000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>487635000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2225,21 +2722,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>624000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>452000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>305000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-1050000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>627000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2248,21 +2746,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>9853000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>8714000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>9271000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>8708000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>7333000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>7340000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2271,21 +2770,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>747000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>470000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-8000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>247000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-1109000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>433000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2294,21 +2794,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>1432000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>1356000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>1361000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>1421000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>1322000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>1409000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2317,21 +2818,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>1335000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>1334000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>1332000000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>1325000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>1322000000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>1316000000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2340,21 +2842,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0.31</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.11</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-0.82</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>0.44</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2363,21 +2866,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.11</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-0.82</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0.45</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2386,21 +2890,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>595000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>423000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>146000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>276000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-1079000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>627000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2408,16 +2913,17 @@
           <t>Average Dilution Earnings</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n">
         <v>29000000</v>
       </c>
-      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2426,21 +2932,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>595000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>423000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>146000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>276000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-1079000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>598000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2464,6 +2971,7 @@
         <v>29000000</v>
       </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2472,21 +2980,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>624000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>452000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>305000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-1050000000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>627000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2495,21 +3004,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>624000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>452000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>305000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-1050000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>627000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2518,21 +3028,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>624000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>452000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>305000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-1050000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>627000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2541,21 +3052,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-19000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-436000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-17000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>106000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2564,21 +3076,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>699000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>433000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-261000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>288000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-1045000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>733000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2587,21 +3100,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-53000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-100000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-408000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-148000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-1378000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>180000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2610,21 +3124,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-78000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-117000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-413000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-180000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-1403000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>163000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2636,18 +3151,19 @@
         <v>0</v>
       </c>
       <c r="C33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>244000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2660,7 +3176,8 @@
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n">
         <v>2000000</v>
       </c>
     </row>
@@ -2670,18 +3187,21 @@
           <t>Impairment Of Capital Assets</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n">
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n">
         <v>260000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>1361000000</v>
       </c>
-      <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2690,21 +3210,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>117000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>156000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>181000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>42000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>81000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2713,21 +3234,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>17000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>32000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>17000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2736,21 +3258,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-73000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>-54000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-261000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>8000000</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>39000000</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>39000000</v>
       </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2759,17 +3282,20 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>73000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>54000000</v>
       </c>
-      <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n">
-        <v>-39000000</v>
-      </c>
+      <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n">
         <v>-39000000</v>
       </c>
       <c r="G39" s="3" t="n">
+        <v>-39000000</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>-5000000</v>
       </c>
     </row>
@@ -2781,12 +3307,13 @@
       </c>
       <c r="B40" s="3" t="n"/>
       <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2795,21 +3322,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>825000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>587000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>408000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>428000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>294000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>514000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2818,21 +3346,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>3075000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>2753000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>2833000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>2244000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>1875000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>1781000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2841,21 +3370,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>323000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>311000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>310000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>126000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>37000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>38000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2864,21 +3394,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>323000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>311000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>310000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>126000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>37000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>38000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2887,21 +3418,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>323000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>311000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>310000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>126000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>37000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>38000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2910,21 +3442,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>323000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>311000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>310000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>126000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>37000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>38000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2933,21 +3466,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>922000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>744000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>881000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>622000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>540000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>475000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2956,21 +3490,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>1830000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>1698000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>1642000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>1496000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>1298000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>1268000000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2979,21 +3514,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>3900000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>3340000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>3241000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>2672000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>2169000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>2295000000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3002,21 +3538,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>6778000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>5961000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>6438000000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>6464000000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>5458000000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>5559000000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3025,21 +3562,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>10678000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>9301000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>9679000000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>9136000000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>7627000000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>7854000000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3048,28 +3586,29 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>10678000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>9301000000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>9679000000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>9136000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>7627000000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>7854000000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4855,7 +5394,1999 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1323294768</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1328922107</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1318292428</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1318814831</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1310531962</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1323294768</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1328922107</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1318292428</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1318814831</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1310531962</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>15954000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>16770000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>16592000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>19082000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>5863000000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>21246000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>21611000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>24077000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>23653000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>17530000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-4356000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-5155000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-5450000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-6002000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>6630000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>46538000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>46385000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>47053000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>48055000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>41397000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2384000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>846000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>351000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-1345000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>7033000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-4356000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-5155000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-5450000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-6002000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>6630000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>1712000000</v>
+      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n">
+        <v>1570000000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>25292000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>24774000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>24688000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>24402000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>23867000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>43529000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>42479000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>42444000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>41256000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>36245000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>25353000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>24834000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>24754000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>24467000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>23927000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>61000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>65000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>25292000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>24774000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>24688000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>24402000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>23867000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-2717000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-2772000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-2748000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-3024000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-3094000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-2717000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-2772000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-2748000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-3024000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-3094000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-2211000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-2593000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-2811000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-2786000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-2892000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>30207000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>30126000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>30234000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>30199000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>29840000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>54159000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>50934000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>51152000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>52873000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>43927000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>27184000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>26577000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>26509000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>25526000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>19389000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>8947000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>8872000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>791000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>8672000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>7011000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n">
+        <v>930000000</v>
+      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n">
+        <v>859000000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n">
+        <v>930000000</v>
+      </c>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n">
+        <v>859000000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>183000000</v>
+      </c>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n">
+        <v>163000000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n">
+        <v>5453000000</v>
+      </c>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n">
+        <v>3951000000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
+        <v>4980000000</v>
+      </c>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n">
+        <v>3578000000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n">
+        <v>473000000</v>
+      </c>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n">
+        <v>373000000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>18237000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>17705000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>19152000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>16854000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>12378000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
+        <v>1396000000</v>
+      </c>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n">
+        <v>1309000000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>18237000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>17705000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>17756000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>16854000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>12378000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>26975000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>24357000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>24643000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>27347000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>24538000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n">
+        <v>32000000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>5621000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>5483000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>5974000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>5311000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>4172000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>5621000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>5483000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>5974000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>5311000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>4172000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>3009000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>3906000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>4925000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>6799000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>5152000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n">
+        <v>316000000</v>
+      </c>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n">
+        <v>261000000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>3009000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>3906000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>4609000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>6799000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>5152000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>2249000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>3071000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>3796000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>5050000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>4374000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Commercial Paper</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>637000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>704000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>681000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>625000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>662000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Current Notes Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>123000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>131000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>132000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>1124000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>116000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1957000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1375000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1871000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1549000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1055000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>16388000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>13593000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>11873000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>13688000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>14159000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>4690000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>4839000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>2742000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>4770000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>4566000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>11698000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>8754000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>9131000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>8918000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>9593000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Payable</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n">
+        <v>90000000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>387000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>375000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1384000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>256000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>277000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>387000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>375000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>319000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>256000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>277000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>11311000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>8379000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>7731000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>8662000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>9316000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>79512000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>75768000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>75906000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>77340000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>67854000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>50153000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>50565000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>50912000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>51338000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>36283000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>13992000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>13801000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>1540000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>13817000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>12674000000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n">
+        <v>2074000000</v>
+      </c>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n">
+        <v>1555000000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>2952000000</v>
+      </c>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n">
+        <v>2396000000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n">
+        <v>2952000000</v>
+      </c>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n">
+        <v>2396000000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Non Current Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>5716000000</v>
+      </c>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n">
+        <v>5583000000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>916000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>924000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>955000000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>999000000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>965000000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>916000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>924000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>955000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>999000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>965000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>29648000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>29929000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>30138000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>30404000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>17237000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>5820000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>6101000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>6368000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>6637000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>512000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>23828000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>23828000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>23770000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>23767000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>16725000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>5597000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>5911000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>7537000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>6118000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>5407000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>-6770000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>-6797000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>-6628000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-6883000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>-6881000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>12367000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>12708000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>14165000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>13001000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>12288000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n">
+        <v>1535000000</v>
+      </c>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n">
+        <v>1408000000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>10207000000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>10343000000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>10246000000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>10607000000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>10505000000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1906000000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>2056000000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>2075000000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>2088000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1717000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>254000000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>309000000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>309000000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>306000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>29359000000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>25203000000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>24994000000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>26002000000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>31571000000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>5053000000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>4683000000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>3753000000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>4835000000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>4002000000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>9034000000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>6913000000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>6352000000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>7163000000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>8096000000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>2824000000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>1984000000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>2213000000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>2708000000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>2988000000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>6210000000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>4929000000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>4139000000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>4455000000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>5108000000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>9980000000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>8766000000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>9116000000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>9433000000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>7806000000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Receivables Adjustments Allowances</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>-24000000</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>-24000000</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>-22000000</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>-18000000</v>
+      </c>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="3" t="n">
+        <v>-9000000</v>
+      </c>
+      <c r="H80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>4085000000</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>4214000000</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>4222000000</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>4191000000</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>4242000000</v>
+      </c>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>5919000000</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>4576000000</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>4916000000</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>5260000000</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>3564000000</v>
+      </c>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n"/>
+      <c r="C83" s="3" t="n"/>
+      <c r="D83" s="3" t="n"/>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="n">
+        <v>-10000000</v>
+      </c>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n"/>
+      <c r="C84" s="3" t="n"/>
+      <c r="D84" s="3" t="n"/>
+      <c r="E84" s="3" t="n"/>
+      <c r="F84" s="3" t="n">
+        <v>3574000000</v>
+      </c>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>5292000000</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>4841000000</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>5773000000</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>4571000000</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>11667000000</v>
+      </c>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>5292000000</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>4841000000</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>5773000000</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>4571000000</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>11667000000</v>
+      </c>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6170,13 +8701,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6186,6 +8717,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6196,30 +8728,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -6232,21 +8769,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>827000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>609000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>1824000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>729000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-1008000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-918000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6255,21 +8793,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-154000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-158000000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-100000000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-52000000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6278,21 +8817,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-2454000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-917000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-5174000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-602000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-575000000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-486000000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6301,21 +8841,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>2104000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>126000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>3855000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>5076000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>152000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>105000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6324,21 +8865,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-583000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-569000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-641000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-576000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-547000000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-528000000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6347,21 +8889,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>5354000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>4925000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>5859000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>4697000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>11788000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>13852000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6370,21 +8913,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>4925000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>5859000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>4697000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>11788000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>13852000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>15105000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6393,21 +8937,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>-42000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>33000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>-30000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>-29000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>81000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>-43000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6416,21 +8961,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>471000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-967000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>1192000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-7062000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-2145000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-1210000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6439,21 +8985,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-739000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-1352000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-1697000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>4235000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-695000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-797000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6462,21 +9009,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-739000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-1352000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-1697000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>4235000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-695000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-797000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6485,21 +9033,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-8000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-2000000</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-8000000</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6508,21 +9057,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-10000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-173000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-60000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-58000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-2000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-169000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6531,10 +9081,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-218000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-219000000</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>-200000000</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>-200000000</v>
@@ -6543,9 +9093,10 @@
         <v>-200000000</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-196000000</v>
+        <v>-200000000</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6566,9 +9117,10 @@
         <v>-29000000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-25000000</v>
+        <v>-29000000</v>
       </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6577,10 +9129,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-189000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-190000000</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>-171000000</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-171000000</v>
@@ -6592,6 +9144,7 @@
         <v>-171000000</v>
       </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6600,21 +9153,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-154000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-158000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-100000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-52000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6623,21 +9177,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-154000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-158000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-100000000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-52000000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6646,21 +9201,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-357000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-794000000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-1335000000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>4493000000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-443000000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-372000000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6669,21 +9225,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-7000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-16000000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>19000000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>9000000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6692,21 +9249,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-350000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-791000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-1319000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>4474000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-423000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-381000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6715,21 +9273,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-2454000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-917000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-5174000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-602000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-575000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-486000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6738,21 +9297,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>2104000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>126000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>3855000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>5076000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>152000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>105000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6761,21 +9321,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-200000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-793000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>424000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-12602000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-989000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-23000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6784,21 +9345,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-200000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-793000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>424000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-12602000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-989000000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-23000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6807,21 +9369,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-288000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>54000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>114000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-561000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>210000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6830,21 +9393,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-2000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>885000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>48000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>39000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>1000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6853,21 +9417,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>887000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>54000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>40000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>1000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6876,21 +9441,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-2000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-6000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6905,15 +9471,16 @@
         <v>0</v>
       </c>
       <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>-12278000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>210000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6934,9 +9501,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>210000000</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6945,13 +9513,14 @@
         </is>
       </c>
       <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n">
         <v>-147000000</v>
       </c>
     </row>
@@ -6962,21 +9531,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-453000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-503000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-515000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-486000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-467000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-444000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6985,21 +9555,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>66000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>126000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>90000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>80000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>84000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7008,21 +9579,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-583000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-569000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-641000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-576000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-547000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-528000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7031,21 +9603,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>1410000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>1178000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>2465000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>1305000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-461000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-390000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7054,21 +9627,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>1410000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1178000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>2465000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>1305000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-461000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-390000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7077,19 +9651,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>51000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>29000000</v>
       </c>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7098,21 +9675,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-545000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-383000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>723000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-66000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-1653000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-1711000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7121,21 +9699,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-851000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>1025000000</v>
       </c>
-      <c r="D41" s="3" t="n">
-        <v>-120000000</v>
-      </c>
       <c r="E41" s="3" t="n">
-        <v>277000000</v>
+        <v>-88000000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-1093000000</v>
+        <v>245000000</v>
       </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7144,21 +9723,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>3117000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>582000000</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>-980000000</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>-980000000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-1551000000</v>
+        <v>-1012000000</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>-215000000</v>
+        <v>-1519000000</v>
       </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7167,19 +9747,20 @@
         </is>
       </c>
       <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n">
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n">
         <v>-12000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>-14000000</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>-16000000</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>-16000000</v>
       </c>
       <c r="G43" s="3" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>-20000000</v>
       </c>
     </row>
@@ -7190,21 +9771,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>3117000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>582000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-968000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>-966000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>-1519000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>-215000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7213,21 +9795,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>3066000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>496000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>-873000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>-897000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>-1434000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>-264000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7236,21 +9819,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>86000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-95000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>-69000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-85000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>49000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7259,21 +9843,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>86000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>-95000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>-69000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>-85000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>49000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7282,21 +9867,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>-2498000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>-458000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>398000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>1820000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>376000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>-811000000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7305,21 +9891,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-1160000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>344000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>280000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>-786000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>-755000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>408000000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7328,21 +9915,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>-1372000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>274000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>430000000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>-758000000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>-463000000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>91000000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7351,21 +9939,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>107000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>77000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>493000000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>117000000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>37000000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>137000000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7374,21 +9963,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>216000000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>196000000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>177000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>116000000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>154000000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7397,21 +9987,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>61000000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>172000000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>149000000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>123000000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>67000000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7420,15 +10011,16 @@
         </is>
       </c>
       <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n">
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
         <v>260000000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7437,21 +10029,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>-115000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>-151000000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>-491000000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>-31000000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>-41000000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>-2000000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7460,21 +10053,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>-115000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>-151000000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>-491000000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>-31000000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>-41000000</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>-2000000</v>
-      </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7483,21 +10077,22 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>877000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>872000000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>877000000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>687000000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>574000000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>599000000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7506,21 +10101,22 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>877000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>872000000</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>877000000</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>687000000</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="F58" s="3" t="n">
         <v>574000000</v>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>599000000</v>
-      </c>
       <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7529,21 +10125,22 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
+        <v>-25000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>-17000000</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="D59" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="E59" s="3" t="n">
         <v>-33000000</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="F59" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="F59" s="3" t="n">
-        <v>-261000000</v>
-      </c>
       <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7553,16 +10150,17 @@
       </c>
       <c r="B60" s="3" t="n"/>
       <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n">
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="F60" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="G60" s="3" t="n">
         <v>77000000</v>
       </c>
-      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7571,21 +10169,22 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
+        <v>-25000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
         <v>-17000000</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="D61" s="3" t="n">
         <v>-16000000</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="E61" s="3" t="n">
         <v>-32000000</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="F61" s="3" t="n">
         <v>-25000000</v>
       </c>
-      <c r="F61" s="3" t="n">
-        <v>-17000000</v>
-      </c>
       <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7597,18 +10196,19 @@
         <v>0</v>
       </c>
       <c r="C62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="E62" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="F62" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F62" s="3" t="n">
-        <v>-244000000</v>
-      </c>
       <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7617,28 +10217,29 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
+        <v>624000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
         <v>452000000</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="D63" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="E63" s="3" t="n">
         <v>305000000</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="F63" s="3" t="n">
         <v>-1050000000</v>
       </c>
-      <c r="F63" s="3" t="n">
-        <v>627000000</v>
-      </c>
       <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7666,12 +10267,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trailing P/E</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>missing from yfinance</t>
+          <t>no gaps detected</t>
         </is>
       </c>
     </row>
